--- a/database/event/6811/event_6811_evp_summary.xlsx
+++ b/database/event/6811/event_6811_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>11.2745</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>7.0962</v>
       </c>
       <c r="D2" t="n">
         <v>4.1333</v>
@@ -545,7 +545,7 @@
         <v>10.1479</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>6.3871</v>
       </c>
       <c r="D3" t="n">
         <v>3.6782</v>
@@ -591,7 +591,7 @@
         <v>7.8843</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>4.9624</v>
       </c>
       <c r="D4" t="n">
         <v>2.7637</v>
@@ -637,7 +637,7 @@
         <v>6.5963</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>4.1517</v>
       </c>
       <c r="D5" t="n">
         <v>2.2434</v>
@@ -683,7 +683,7 @@
         <v>6.3048</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>3.9682</v>
       </c>
       <c r="D6" t="n">
         <v>2.1256</v>
@@ -729,7 +729,7 @@
         <v>6.2061</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>3.9061</v>
       </c>
       <c r="D7" t="n">
         <v>2.0858</v>
@@ -775,7 +775,7 @@
         <v>5.4038</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>3.4011</v>
       </c>
       <c r="D8" t="n">
         <v>1.7617</v>
@@ -821,7 +821,7 @@
         <v>4.6365</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2.9182</v>
       </c>
       <c r="D9" t="n">
         <v>1.4517</v>
@@ -867,7 +867,7 @@
         <v>3.5591</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2.2401</v>
       </c>
       <c r="D10" t="n">
         <v>1.0164</v>
@@ -913,7 +913,7 @@
         <v>3.4115</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2.1472</v>
       </c>
       <c r="D11" t="n">
         <v>0.9568</v>
@@ -959,7 +959,7 @@
         <v>3.157</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1.987</v>
       </c>
       <c r="D12" t="n">
         <v>0.854</v>
@@ -1005,7 +1005,7 @@
         <v>2.9266</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1.842</v>
       </c>
       <c r="D13" t="n">
         <v>0.7609</v>
@@ -1051,7 +1051,7 @@
         <v>2.9213</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1.8387</v>
       </c>
       <c r="D14" t="n">
         <v>0.7588</v>
@@ -1097,7 +1097,7 @@
         <v>2.9038</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1.8276</v>
       </c>
       <c r="D15" t="n">
         <v>0.7517</v>
@@ -1143,7 +1143,7 @@
         <v>2.75</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1.7308</v>
       </c>
       <c r="D16" t="n">
         <v>0.6896</v>
@@ -1189,7 +1189,7 @@
         <v>2.5552</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1.6082</v>
       </c>
       <c r="D17" t="n">
         <v>0.6109</v>
@@ -1235,7 +1235,7 @@
         <v>2.4914</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1.5681</v>
       </c>
       <c r="D18" t="n">
         <v>0.5851</v>
@@ -1281,7 +1281,7 @@
         <v>2.475</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1.5578</v>
       </c>
       <c r="D19" t="n">
         <v>0.5785</v>
@@ -1327,7 +1327,7 @@
         <v>2.4664</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1.5524</v>
       </c>
       <c r="D20" t="n">
         <v>0.575</v>
@@ -1373,7 +1373,7 @@
         <v>2.2699</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.4287</v>
       </c>
       <c r="D21" t="n">
         <v>0.4956</v>
@@ -1419,7 +1419,7 @@
         <v>2.1141</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1.3306</v>
       </c>
       <c r="D22" t="n">
         <v>0.4327</v>
@@ -1465,7 +1465,7 @@
         <v>2.1118</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1.3292</v>
       </c>
       <c r="D23" t="n">
         <v>0.4318</v>
@@ -1511,7 +1511,7 @@
         <v>1.6896</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1.0634</v>
       </c>
       <c r="D24" t="n">
         <v>0.2612</v>
@@ -1557,7 +1557,7 @@
         <v>1.6524</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="D25" t="n">
         <v>0.2462</v>
@@ -1603,7 +1603,7 @@
         <v>1.553</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.9775</v>
       </c>
       <c r="D26" t="n">
         <v>0.206</v>
@@ -1649,7 +1649,7 @@
         <v>1.4062</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.8851</v>
       </c>
       <c r="D27" t="n">
         <v>0.1467</v>
@@ -1695,7 +1695,7 @@
         <v>1.4023</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="D28" t="n">
         <v>0.1451</v>
@@ -1741,7 +1741,7 @@
         <v>1.3864</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.8726</v>
       </c>
       <c r="D29" t="n">
         <v>0.1387</v>
@@ -1787,7 +1787,7 @@
         <v>1.3366</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.8413</v>
       </c>
       <c r="D30" t="n">
         <v>0.1186</v>
@@ -1833,7 +1833,7 @@
         <v>1.1372</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.7158</v>
       </c>
       <c r="D31" t="n">
         <v>0.038</v>
@@ -1879,7 +1879,7 @@
         <v>0.9979</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.6281</v>
       </c>
       <c r="D32" t="n">
         <v>-0.0182</v>
@@ -1925,7 +1925,7 @@
         <v>0.9403</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.5918</v>
       </c>
       <c r="D33" t="n">
         <v>-0.0415</v>
@@ -1971,7 +1971,7 @@
         <v>0.8424</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.5302</v>
       </c>
       <c r="D34" t="n">
         <v>-0.08110000000000001</v>
@@ -2017,7 +2017,7 @@
         <v>0.8056</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.507</v>
       </c>
       <c r="D35" t="n">
         <v>-0.0959</v>
@@ -2063,7 +2063,7 @@
         <v>0.6801</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.4281</v>
       </c>
       <c r="D36" t="n">
         <v>-0.1466</v>
@@ -2109,7 +2109,7 @@
         <v>0.6412</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.4036</v>
       </c>
       <c r="D37" t="n">
         <v>-0.1623</v>
@@ -2155,7 +2155,7 @@
         <v>0.5371</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.3381</v>
       </c>
       <c r="D38" t="n">
         <v>-0.2044</v>
@@ -2201,7 +2201,7 @@
         <v>0.5133</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.3231</v>
       </c>
       <c r="D39" t="n">
         <v>-0.214</v>
@@ -2247,7 +2247,7 @@
         <v>0.4723</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.2973</v>
       </c>
       <c r="D40" t="n">
         <v>-0.2306</v>
@@ -2293,7 +2293,7 @@
         <v>0.4142</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.2607</v>
       </c>
       <c r="D41" t="n">
         <v>-0.254</v>
@@ -2339,7 +2339,7 @@
         <v>0.33</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.2077</v>
       </c>
       <c r="D42" t="n">
         <v>-0.288</v>
@@ -2385,7 +2385,7 @@
         <v>0.2285</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.1438</v>
       </c>
       <c r="D43" t="n">
         <v>-0.3291</v>
@@ -2431,7 +2431,7 @@
         <v>0.2125</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.1337</v>
       </c>
       <c r="D44" t="n">
         <v>-0.3355</v>
@@ -2477,7 +2477,7 @@
         <v>0.1053</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.0663</v>
       </c>
       <c r="D45" t="n">
         <v>-0.3788</v>
@@ -2523,7 +2523,7 @@
         <v>0.0697</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.0439</v>
       </c>
       <c r="D46" t="n">
         <v>-0.3932</v>
@@ -2569,7 +2569,7 @@
         <v>0.0619</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.039</v>
       </c>
       <c r="D47" t="n">
         <v>-0.3964</v>
@@ -2615,7 +2615,7 @@
         <v>0.0537</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.0338</v>
       </c>
       <c r="D48" t="n">
         <v>-0.3997</v>
@@ -2661,7 +2661,7 @@
         <v>0.0225</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.0142</v>
       </c>
       <c r="D49" t="n">
         <v>-0.4123</v>
@@ -2707,7 +2707,7 @@
         <v>0.008500000000000001</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.0053</v>
       </c>
       <c r="D50" t="n">
         <v>-0.4179</v>
@@ -2753,7 +2753,7 @@
         <v>-0.0283</v>
       </c>
       <c r="C51" t="n">
-        <v>-0</v>
+        <v>-0.0178</v>
       </c>
       <c r="D51" t="n">
         <v>-0.4328</v>
@@ -2799,7 +2799,7 @@
         <v>-0.0822</v>
       </c>
       <c r="C52" t="n">
-        <v>-0</v>
+        <v>-0.0517</v>
       </c>
       <c r="D52" t="n">
         <v>-0.4546</v>
@@ -2845,7 +2845,7 @@
         <v>-0.0893</v>
       </c>
       <c r="C53" t="n">
-        <v>-0</v>
+        <v>-0.0562</v>
       </c>
       <c r="D53" t="n">
         <v>-0.4574</v>
@@ -2891,7 +2891,7 @@
         <v>-0.2046</v>
       </c>
       <c r="C54" t="n">
-        <v>-0</v>
+        <v>-0.1288</v>
       </c>
       <c r="D54" t="n">
         <v>-0.504</v>
@@ -2937,7 +2937,7 @@
         <v>-0.2669</v>
       </c>
       <c r="C55" t="n">
-        <v>-0</v>
+        <v>-0.168</v>
       </c>
       <c r="D55" t="n">
         <v>-0.5292</v>
@@ -2983,7 +2983,7 @@
         <v>-0.376</v>
       </c>
       <c r="C56" t="n">
-        <v>-0</v>
+        <v>-0.2367</v>
       </c>
       <c r="D56" t="n">
         <v>-0.5733</v>
@@ -3029,7 +3029,7 @@
         <v>-0.407</v>
       </c>
       <c r="C57" t="n">
-        <v>-0</v>
+        <v>-0.2562</v>
       </c>
       <c r="D57" t="n">
         <v>-0.5858</v>
@@ -3075,7 +3075,7 @@
         <v>-0.4554</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.2866</v>
       </c>
       <c r="D58" t="n">
         <v>-0.6052999999999999</v>
@@ -3121,7 +3121,7 @@
         <v>-0.519</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.3267</v>
       </c>
       <c r="D59" t="n">
         <v>-0.631</v>
@@ -3167,7 +3167,7 @@
         <v>-0.5909</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.3719</v>
       </c>
       <c r="D60" t="n">
         <v>-0.6601</v>
@@ -3213,7 +3213,7 @@
         <v>-0.6169</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.3883</v>
       </c>
       <c r="D61" t="n">
         <v>-0.6706</v>
@@ -3259,7 +3259,7 @@
         <v>-0.6567</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.4133</v>
       </c>
       <c r="D62" t="n">
         <v>-0.6867</v>
@@ -3305,7 +3305,7 @@
         <v>-0.6983</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.4395</v>
       </c>
       <c r="D63" t="n">
         <v>-0.7035</v>
@@ -3351,7 +3351,7 @@
         <v>-0.7302</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.4596</v>
       </c>
       <c r="D64" t="n">
         <v>-0.7163</v>
@@ -3397,7 +3397,7 @@
         <v>-0.7338</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.4619</v>
       </c>
       <c r="D65" t="n">
         <v>-0.7178</v>
@@ -3443,7 +3443,7 @@
         <v>-0.7375</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.4642</v>
       </c>
       <c r="D66" t="n">
         <v>-0.7193000000000001</v>
@@ -3489,7 +3489,7 @@
         <v>-0.9607</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.6047</v>
       </c>
       <c r="D67" t="n">
         <v>-0.8095</v>
@@ -3535,7 +3535,7 @@
         <v>-0.9892</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.6226</v>
       </c>
       <c r="D68" t="n">
         <v>-0.821</v>
@@ -3581,7 +3581,7 @@
         <v>-1.1224</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.7064</v>
       </c>
       <c r="D69" t="n">
         <v>-0.8748</v>
@@ -3627,7 +3627,7 @@
         <v>-1.1388</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.7168</v>
       </c>
       <c r="D70" t="n">
         <v>-0.8814</v>
@@ -3673,7 +3673,7 @@
         <v>-1.4046</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-0.8841</v>
       </c>
       <c r="D71" t="n">
         <v>-0.9888</v>
@@ -3719,7 +3719,7 @@
         <v>-1.6658</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-1.0485</v>
       </c>
       <c r="D72" t="n">
         <v>-1.0943</v>
@@ -3765,7 +3765,7 @@
         <v>-1.7399</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-1.0951</v>
       </c>
       <c r="D73" t="n">
         <v>-1.1242</v>
@@ -3811,7 +3811,7 @@
         <v>-1.7982</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-1.1318</v>
       </c>
       <c r="D74" t="n">
         <v>-1.1478</v>
@@ -3857,7 +3857,7 @@
         <v>-1.881</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-1.1839</v>
       </c>
       <c r="D75" t="n">
         <v>-1.1812</v>
@@ -3903,7 +3903,7 @@
         <v>-1.9526</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-1.229</v>
       </c>
       <c r="D76" t="n">
         <v>-1.2102</v>
@@ -3949,7 +3949,7 @@
         <v>-2.1076</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-1.3265</v>
       </c>
       <c r="D77" t="n">
         <v>-1.2728</v>
@@ -3995,7 +3995,7 @@
         <v>-2.1675</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-1.3642</v>
       </c>
       <c r="D78" t="n">
         <v>-1.297</v>
@@ -4041,7 +4041,7 @@
         <v>-2.6157</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-1.6463</v>
       </c>
       <c r="D79" t="n">
         <v>-1.478</v>
@@ -4087,7 +4087,7 @@
         <v>-3.5401</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-2.2281</v>
       </c>
       <c r="D80" t="n">
         <v>-1.8515</v>
@@ -4133,7 +4133,7 @@
         <v>-3.6564</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-2.3013</v>
       </c>
       <c r="D81" t="n">
         <v>-1.8985</v>
@@ -4179,7 +4179,7 @@
         <v>-3.6743</v>
       </c>
       <c r="C82" t="n">
-        <v>-0</v>
+        <v>-2.3126</v>
       </c>
       <c r="D82" t="n">
         <v>-1.9057</v>

--- a/database/event/6811/event_6811_evp_summary.xlsx
+++ b/database/event/6811/event_6811_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>7.0962</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1333</v>
+        <v>4.0479</v>
       </c>
       <c r="E2" t="n">
         <v>11.2745</v>
@@ -548,7 +548,7 @@
         <v>6.3871</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6782</v>
+        <v>3.599</v>
       </c>
       <c r="E3" t="n">
         <v>10.1479</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.8843</v>
+        <v>7.7894</v>
       </c>
       <c r="C4" t="n">
-        <v>4.9624</v>
+        <v>4.9026</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7637</v>
+        <v>2.6594</v>
       </c>
       <c r="E4" t="n">
-        <v>7.8843</v>
+        <v>7.7894</v>
       </c>
       <c r="F4" t="n">
-        <v>5.1431</v>
+        <v>5.0482</v>
       </c>
       <c r="G4" t="n">
         <v>2.7412</v>
       </c>
       <c r="H4" t="n">
-        <v>5.7613</v>
+        <v>5.6125</v>
       </c>
       <c r="I4" t="n">
         <v>5.9516</v>
@@ -640,7 +640,7 @@
         <v>4.1517</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2434</v>
+        <v>2.1841</v>
       </c>
       <c r="E5" t="n">
         <v>6.5963</v>
@@ -686,7 +686,7 @@
         <v>3.9682</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1256</v>
+        <v>2.0679</v>
       </c>
       <c r="E6" t="n">
         <v>6.3048</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.2061</v>
+        <v>6.1342</v>
       </c>
       <c r="C7" t="n">
-        <v>3.9061</v>
+        <v>3.8609</v>
       </c>
       <c r="D7" t="n">
-        <v>2.0858</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>6.2061</v>
+        <v>6.1342</v>
       </c>
       <c r="F7" t="n">
-        <v>3.8817</v>
+        <v>3.8098</v>
       </c>
       <c r="G7" t="n">
         <v>2.3244</v>
       </c>
       <c r="H7" t="n">
-        <v>3.8817</v>
+        <v>3.8098</v>
       </c>
       <c r="I7" t="n">
         <v>3.9729</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.4038</v>
+        <v>5.3047</v>
       </c>
       <c r="C8" t="n">
-        <v>3.4011</v>
+        <v>3.3388</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7617</v>
+        <v>1.6695</v>
       </c>
       <c r="E8" t="n">
-        <v>5.4038</v>
+        <v>5.3047</v>
       </c>
       <c r="F8" t="n">
-        <v>3.839</v>
+        <v>3.7399</v>
       </c>
       <c r="G8" t="n">
         <v>1.5648</v>
       </c>
       <c r="H8" t="n">
-        <v>3.839</v>
+        <v>3.7399</v>
       </c>
       <c r="I8" t="n">
         <v>3.9658</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.6365</v>
+        <v>4.5336</v>
       </c>
       <c r="C9" t="n">
-        <v>2.9182</v>
+        <v>2.8534</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4517</v>
+        <v>1.3623</v>
       </c>
       <c r="E9" t="n">
-        <v>4.6365</v>
+        <v>4.5336</v>
       </c>
       <c r="F9" t="n">
-        <v>3.9835</v>
+        <v>3.8806</v>
       </c>
       <c r="G9" t="n">
         <v>0.653</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9835</v>
+        <v>3.8806</v>
       </c>
       <c r="I9" t="n">
         <v>4.1151</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.5591</v>
+        <v>3.5024</v>
       </c>
       <c r="C10" t="n">
-        <v>2.2401</v>
+        <v>2.2044</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0164</v>
+        <v>0.9514</v>
       </c>
       <c r="E10" t="n">
-        <v>3.5591</v>
+        <v>3.5024</v>
       </c>
       <c r="F10" t="n">
-        <v>3.0637</v>
+        <v>3.007</v>
       </c>
       <c r="G10" t="n">
         <v>0.4954</v>
       </c>
       <c r="H10" t="n">
-        <v>3.0637</v>
+        <v>3.007</v>
       </c>
       <c r="I10" t="n">
         <v>3.1357</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.4115</v>
+        <v>3.3111</v>
       </c>
       <c r="C11" t="n">
-        <v>2.1472</v>
+        <v>2.084</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9568</v>
+        <v>0.8752</v>
       </c>
       <c r="E11" t="n">
-        <v>3.4115</v>
+        <v>3.3111</v>
       </c>
       <c r="F11" t="n">
-        <v>3.8875</v>
+        <v>3.7871</v>
       </c>
       <c r="G11" t="n">
         <v>-0.476</v>
       </c>
       <c r="H11" t="n">
-        <v>3.8875</v>
+        <v>3.7871</v>
       </c>
       <c r="I11" t="n">
         <v>4.016</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.157</v>
+        <v>3.0986</v>
       </c>
       <c r="C12" t="n">
-        <v>1.987</v>
+        <v>1.9503</v>
       </c>
       <c r="D12" t="n">
-        <v>0.854</v>
+        <v>0.7906</v>
       </c>
       <c r="E12" t="n">
-        <v>3.157</v>
+        <v>3.0986</v>
       </c>
       <c r="F12" t="n">
-        <v>3.157</v>
+        <v>3.0986</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3.157</v>
+        <v>3.0986</v>
       </c>
       <c r="I12" t="n">
         <v>3.2312</v>
@@ -1008,7 +1008,7 @@
         <v>1.842</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7609</v>
+        <v>0.722</v>
       </c>
       <c r="E13" t="n">
         <v>2.9266</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.9213</v>
+        <v>2.8881</v>
       </c>
       <c r="C14" t="n">
-        <v>1.8387</v>
+        <v>1.8178</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7588</v>
+        <v>0.7067</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9213</v>
+        <v>2.8881</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7946</v>
+        <v>1.7614</v>
       </c>
       <c r="G14" t="n">
         <v>1.1267</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7946</v>
+        <v>1.7614</v>
       </c>
       <c r="I14" t="n">
         <v>1.8368</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.9038</v>
+        <v>2.8714</v>
       </c>
       <c r="C15" t="n">
-        <v>1.8276</v>
+        <v>1.8073</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7517</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9038</v>
+        <v>2.8714</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9038</v>
+        <v>2.8714</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.9038</v>
+        <v>2.8714</v>
       </c>
       <c r="I15" t="n">
         <v>2.9445</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.75</v>
+        <v>2.6991</v>
       </c>
       <c r="C16" t="n">
-        <v>1.7308</v>
+        <v>1.6988</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6896</v>
+        <v>0.6314</v>
       </c>
       <c r="E16" t="n">
-        <v>2.75</v>
+        <v>2.6991</v>
       </c>
       <c r="F16" t="n">
-        <v>2.75</v>
+        <v>2.6991</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.75</v>
+        <v>2.6991</v>
       </c>
       <c r="I16" t="n">
         <v>2.8146</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.5552</v>
+        <v>2.5052</v>
       </c>
       <c r="C17" t="n">
-        <v>1.6082</v>
+        <v>1.5768</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6109</v>
+        <v>0.5542</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5552</v>
+        <v>2.5052</v>
       </c>
       <c r="F17" t="n">
-        <v>2.7038</v>
+        <v>2.6538</v>
       </c>
       <c r="G17" t="n">
         <v>-0.1486</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7038</v>
+        <v>2.6538</v>
       </c>
       <c r="I17" t="n">
         <v>2.7673</v>
@@ -1228,139 +1228,139 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.4914</v>
+        <v>2.4481</v>
       </c>
       <c r="C18" t="n">
-        <v>1.5681</v>
+        <v>1.5408</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5851</v>
+        <v>0.5314</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4914</v>
+        <v>2.4481</v>
       </c>
       <c r="F18" t="n">
-        <v>2.429</v>
+        <v>2.4481</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0624</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.429</v>
+        <v>2.4481</v>
       </c>
       <c r="I18" t="n">
-        <v>2.4861</v>
+        <v>2.4894</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0624</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>232</v>
+        <v>145</v>
       </c>
       <c r="L18" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.5485</v>
+        <v>2.4894</v>
       </c>
       <c r="N18" t="n">
-        <v>282</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.475</v>
+        <v>2.4465</v>
       </c>
       <c r="C19" t="n">
-        <v>1.5578</v>
+        <v>1.5398</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5785</v>
+        <v>0.5308</v>
       </c>
       <c r="E19" t="n">
-        <v>2.475</v>
+        <v>2.4465</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1942</v>
+        <v>2.3841</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2808</v>
+        <v>0.0624</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1942</v>
+        <v>2.3841</v>
       </c>
       <c r="I19" t="n">
-        <v>2.2667</v>
+        <v>2.4861</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2808</v>
+        <v>0.0624</v>
       </c>
       <c r="K19" t="n">
-        <v>319</v>
+        <v>232</v>
       </c>
       <c r="L19" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="M19" t="n">
-        <v>2.5475</v>
+        <v>2.5485</v>
       </c>
       <c r="N19" t="n">
-        <v>382</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.4664</v>
+        <v>2.4183</v>
       </c>
       <c r="C20" t="n">
-        <v>1.5524</v>
+        <v>1.5221</v>
       </c>
       <c r="D20" t="n">
-        <v>0.575</v>
+        <v>0.5195</v>
       </c>
       <c r="E20" t="n">
-        <v>2.4664</v>
+        <v>2.4183</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4664</v>
+        <v>2.1375</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.2808</v>
       </c>
       <c r="H20" t="n">
-        <v>2.4664</v>
+        <v>2.1375</v>
       </c>
       <c r="I20" t="n">
-        <v>2.4894</v>
+        <v>2.2667</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.2808</v>
       </c>
       <c r="K20" t="n">
-        <v>145</v>
+        <v>319</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M20" t="n">
-        <v>2.4894</v>
+        <v>2.5475</v>
       </c>
       <c r="N20" t="n">
-        <v>145</v>
+        <v>382</v>
       </c>
     </row>
     <row r="21">
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.2699</v>
+        <v>2.2279</v>
       </c>
       <c r="C21" t="n">
-        <v>1.4287</v>
+        <v>1.4022</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4956</v>
+        <v>0.4437</v>
       </c>
       <c r="E21" t="n">
-        <v>2.2699</v>
+        <v>2.2279</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2699</v>
+        <v>2.2279</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.2699</v>
+        <v>2.2279</v>
       </c>
       <c r="I21" t="n">
         <v>2.3232</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.1141</v>
+        <v>2.062</v>
       </c>
       <c r="C22" t="n">
-        <v>1.3306</v>
+        <v>1.2978</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4327</v>
+        <v>0.3776</v>
       </c>
       <c r="E22" t="n">
-        <v>2.1141</v>
+        <v>2.062</v>
       </c>
       <c r="F22" t="n">
-        <v>2.8169</v>
+        <v>2.7648</v>
       </c>
       <c r="G22" t="n">
         <v>-0.7028</v>
       </c>
       <c r="H22" t="n">
-        <v>2.8169</v>
+        <v>2.7648</v>
       </c>
       <c r="I22" t="n">
         <v>2.8831</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.1118</v>
+        <v>2.0548</v>
       </c>
       <c r="C23" t="n">
-        <v>1.3292</v>
+        <v>1.2933</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4318</v>
+        <v>0.3747</v>
       </c>
       <c r="E23" t="n">
-        <v>2.1118</v>
+        <v>2.0548</v>
       </c>
       <c r="F23" t="n">
-        <v>3.0752</v>
+        <v>3.0182</v>
       </c>
       <c r="G23" t="n">
         <v>-0.9634</v>
       </c>
       <c r="H23" t="n">
-        <v>3.0752</v>
+        <v>3.0182</v>
       </c>
       <c r="I23" t="n">
         <v>3.1474</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.6896</v>
+        <v>1.6771</v>
       </c>
       <c r="C24" t="n">
-        <v>1.0634</v>
+        <v>1.0556</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2612</v>
+        <v>0.2242</v>
       </c>
       <c r="E24" t="n">
-        <v>1.6896</v>
+        <v>1.6771</v>
       </c>
       <c r="F24" t="n">
-        <v>1.6896</v>
+        <v>1.6771</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.6896</v>
+        <v>1.6771</v>
       </c>
       <c r="I24" t="n">
         <v>1.7054</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.6524</v>
+        <v>1.6401</v>
       </c>
       <c r="C25" t="n">
-        <v>1.04</v>
+        <v>1.0323</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2462</v>
+        <v>0.2095</v>
       </c>
       <c r="E25" t="n">
-        <v>1.6524</v>
+        <v>1.6401</v>
       </c>
       <c r="F25" t="n">
-        <v>1.6524</v>
+        <v>1.6401</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.6524</v>
+        <v>1.6401</v>
       </c>
       <c r="I25" t="n">
         <v>1.6678</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.553</v>
+        <v>1.5414</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9775</v>
+        <v>0.9702</v>
       </c>
       <c r="D26" t="n">
-        <v>0.206</v>
+        <v>0.1702</v>
       </c>
       <c r="E26" t="n">
-        <v>1.553</v>
+        <v>1.5414</v>
       </c>
       <c r="F26" t="n">
-        <v>1.553</v>
+        <v>1.5414</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.553</v>
+        <v>1.5414</v>
       </c>
       <c r="I26" t="n">
         <v>1.5675</v>
@@ -1642,139 +1642,139 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>isak</t>
+          <t>KEi</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.4062</v>
+        <v>1.3919</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8851</v>
+        <v>0.8761</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1467</v>
+        <v>0.1106</v>
       </c>
       <c r="E27" t="n">
-        <v>1.4062</v>
+        <v>1.3919</v>
       </c>
       <c r="F27" t="n">
-        <v>1.4062</v>
+        <v>1.3919</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.4062</v>
+        <v>1.3919</v>
       </c>
       <c r="I27" t="n">
-        <v>1.4392</v>
+        <v>1.4154</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>308</v>
+        <v>163</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.4392</v>
+        <v>1.4154</v>
       </c>
       <c r="N27" t="n">
-        <v>308</v>
+        <v>163</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KEi</t>
+          <t>Buzz</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.4023</v>
+        <v>1.3915</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8826000000000001</v>
+        <v>0.8758</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1451</v>
+        <v>0.1105</v>
       </c>
       <c r="E28" t="n">
-        <v>1.4023</v>
+        <v>1.3915</v>
       </c>
       <c r="F28" t="n">
-        <v>1.4023</v>
+        <v>-0.1896</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1.581</v>
       </c>
       <c r="H28" t="n">
-        <v>1.4023</v>
+        <v>-0.1896</v>
       </c>
       <c r="I28" t="n">
-        <v>1.4154</v>
+        <v>-0.201</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1.581</v>
       </c>
       <c r="K28" t="n">
-        <v>163</v>
+        <v>278</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="M28" t="n">
-        <v>1.4154</v>
+        <v>1.38</v>
       </c>
       <c r="N28" t="n">
-        <v>163</v>
+        <v>381</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Buzz</t>
+          <t>isak</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.3864</v>
+        <v>1.3801</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8726</v>
+        <v>0.8686</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1387</v>
+        <v>0.1059</v>
       </c>
       <c r="E29" t="n">
-        <v>1.3864</v>
+        <v>1.3801</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1946</v>
+        <v>1.3801</v>
       </c>
       <c r="G29" t="n">
-        <v>1.581</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1946</v>
+        <v>1.3801</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.201</v>
+        <v>1.4392</v>
       </c>
       <c r="J29" t="n">
-        <v>1.581</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>278</v>
+        <v>308</v>
       </c>
       <c r="L29" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.38</v>
+        <v>1.4392</v>
       </c>
       <c r="N29" t="n">
-        <v>381</v>
+        <v>308</v>
       </c>
     </row>
     <row r="30">
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.3366</v>
+        <v>1.2787</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8413</v>
+        <v>0.8048</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1186</v>
+        <v>0.0655</v>
       </c>
       <c r="E30" t="n">
-        <v>1.3366</v>
+        <v>1.2787</v>
       </c>
       <c r="F30" t="n">
-        <v>2.2428</v>
+        <v>2.1849</v>
       </c>
       <c r="G30" t="n">
         <v>-0.9062</v>
       </c>
       <c r="H30" t="n">
-        <v>2.2428</v>
+        <v>2.1849</v>
       </c>
       <c r="I30" t="n">
         <v>2.3169</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.1372</v>
+        <v>1.1161</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7158</v>
+        <v>0.7025</v>
       </c>
       <c r="D31" t="n">
-        <v>0.038</v>
+        <v>0.0007</v>
       </c>
       <c r="E31" t="n">
-        <v>1.1372</v>
+        <v>1.1161</v>
       </c>
       <c r="F31" t="n">
-        <v>1.1372</v>
+        <v>1.1161</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.1372</v>
+        <v>1.1161</v>
       </c>
       <c r="I31" t="n">
         <v>1.1639</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.9979</v>
+        <v>0.9905</v>
       </c>
       <c r="C32" t="n">
-        <v>0.6281</v>
+        <v>0.6234</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0182</v>
+        <v>-0.0493</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9979</v>
+        <v>0.9905</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9979</v>
+        <v>0.9905</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9979</v>
+        <v>0.9905</v>
       </c>
       <c r="I32" t="n">
         <v>1.0072</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9403</v>
+        <v>0.9333</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5918</v>
+        <v>0.5874</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0415</v>
+        <v>-0.0721</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9403</v>
+        <v>0.9333</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9403</v>
+        <v>0.9333</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9403</v>
+        <v>0.9333</v>
       </c>
       <c r="I33" t="n">
         <v>0.949</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8424</v>
+        <v>0.8268</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5302</v>
+        <v>0.5204</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.08110000000000001</v>
+        <v>-0.1145</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8424</v>
+        <v>0.8268</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8424</v>
+        <v>0.8268</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8424</v>
+        <v>0.8268</v>
       </c>
       <c r="I34" t="n">
         <v>0.8622</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8056</v>
+        <v>0.7966</v>
       </c>
       <c r="C35" t="n">
-        <v>0.507</v>
+        <v>0.5014</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0959</v>
+        <v>-0.1265</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8056</v>
+        <v>0.7966</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8056</v>
+        <v>0.7966</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8056</v>
+        <v>0.7966</v>
       </c>
       <c r="I35" t="n">
         <v>0.8169</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6801</v>
+        <v>0.675</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4281</v>
+        <v>0.4248</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1466</v>
+        <v>-0.175</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6801</v>
+        <v>0.675</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6801</v>
+        <v>0.675</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6801</v>
+        <v>0.675</v>
       </c>
       <c r="I36" t="n">
         <v>0.6864</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6412</v>
+        <v>0.6364</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4036</v>
+        <v>0.4005</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1623</v>
+        <v>-0.1904</v>
       </c>
       <c r="E37" t="n">
-        <v>0.6412</v>
+        <v>0.6364</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6412</v>
+        <v>0.6364</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6412</v>
+        <v>0.6364</v>
       </c>
       <c r="I37" t="n">
         <v>0.6472</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5371</v>
+        <v>0.5331</v>
       </c>
       <c r="C38" t="n">
-        <v>0.3381</v>
+        <v>0.3355</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2044</v>
+        <v>-0.2315</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5371</v>
+        <v>0.5331</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5371</v>
+        <v>0.5331</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5371</v>
+        <v>0.5331</v>
       </c>
       <c r="I38" t="n">
         <v>0.5421</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5133</v>
+        <v>0.5155</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3231</v>
+        <v>0.3245</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.214</v>
+        <v>-0.2385</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5133</v>
+        <v>0.5155</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.0828</v>
       </c>
       <c r="G39" t="n">
         <v>0.5983000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.0828</v>
       </c>
       <c r="I39" t="n">
         <v>-0.0878</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4723</v>
+        <v>0.4688</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2973</v>
+        <v>0.2951</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2306</v>
+        <v>-0.2571</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4723</v>
+        <v>0.4688</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4723</v>
+        <v>0.4688</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.4723</v>
+        <v>0.4688</v>
       </c>
       <c r="I40" t="n">
         <v>0.4767</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4142</v>
+        <v>0.3922</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2607</v>
+        <v>0.2469</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.254</v>
+        <v>-0.2877</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4142</v>
+        <v>0.3922</v>
       </c>
       <c r="F41" t="n">
-        <v>1.1911</v>
+        <v>1.1691</v>
       </c>
       <c r="G41" t="n">
         <v>-0.7769</v>
       </c>
       <c r="H41" t="n">
-        <v>1.1911</v>
+        <v>1.1691</v>
       </c>
       <c r="I41" t="n">
         <v>1.2191</v>
@@ -2336,25 +2336,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.33</v>
+        <v>0.3276</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2077</v>
+        <v>0.2062</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.288</v>
+        <v>-0.3134</v>
       </c>
       <c r="E42" t="n">
-        <v>0.33</v>
+        <v>0.3276</v>
       </c>
       <c r="F42" t="n">
-        <v>0.33</v>
+        <v>0.3276</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.33</v>
+        <v>0.3276</v>
       </c>
       <c r="I42" t="n">
         <v>0.3331</v>
@@ -2382,25 +2382,25 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.2285</v>
+        <v>0.2259</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1438</v>
+        <v>0.1422</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3291</v>
+        <v>-0.3539</v>
       </c>
       <c r="E43" t="n">
-        <v>0.2285</v>
+        <v>0.2259</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2285</v>
+        <v>0.2259</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2285</v>
+        <v>0.2259</v>
       </c>
       <c r="I43" t="n">
         <v>0.2317</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2125</v>
+        <v>0.2109</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1337</v>
+        <v>0.1327</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3355</v>
+        <v>-0.3599</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2125</v>
+        <v>0.2109</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2125</v>
+        <v>0.2109</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2125</v>
+        <v>0.2109</v>
       </c>
       <c r="I44" t="n">
         <v>0.2145</v>
@@ -2480,7 +2480,7 @@
         <v>0.0663</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3788</v>
+        <v>-0.402</v>
       </c>
       <c r="E45" t="n">
         <v>0.1053</v>
@@ -2520,25 +2520,25 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.0697</v>
+        <v>0.0692</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0439</v>
+        <v>0.0436</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3932</v>
+        <v>-0.4163</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0697</v>
+        <v>0.0692</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0697</v>
+        <v>0.0692</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0697</v>
+        <v>0.0692</v>
       </c>
       <c r="I46" t="n">
         <v>0.0704</v>
@@ -2566,25 +2566,25 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.0619</v>
+        <v>0.0614</v>
       </c>
       <c r="C47" t="n">
-        <v>0.039</v>
+        <v>0.0386</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3964</v>
+        <v>-0.4194</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0619</v>
+        <v>0.0614</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0619</v>
+        <v>0.0614</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0619</v>
+        <v>0.0614</v>
       </c>
       <c r="I47" t="n">
         <v>0.0624</v>
@@ -2612,25 +2612,25 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.0537</v>
+        <v>0.0535</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0338</v>
+        <v>0.0337</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3997</v>
+        <v>-0.4226</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0537</v>
+        <v>0.0535</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0537</v>
+        <v>0.0535</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0537</v>
+        <v>0.0535</v>
       </c>
       <c r="I48" t="n">
         <v>0.054</v>
@@ -2658,25 +2658,25 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.0225</v>
+        <v>0.0224</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0142</v>
+        <v>0.0141</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4123</v>
+        <v>-0.435</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0225</v>
+        <v>0.0224</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0225</v>
+        <v>0.0224</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0225</v>
+        <v>0.0224</v>
       </c>
       <c r="I49" t="n">
         <v>0.0226</v>
@@ -2710,7 +2710,7 @@
         <v>0.0053</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4179</v>
+        <v>-0.4405</v>
       </c>
       <c r="E50" t="n">
         <v>0.008500000000000001</v>
@@ -2750,25 +2750,25 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.0283</v>
+        <v>-0.0281</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.0178</v>
+        <v>-0.0177</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4328</v>
+        <v>-0.4551</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.0283</v>
+        <v>-0.0281</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.0283</v>
+        <v>-0.0281</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.0283</v>
+        <v>-0.0281</v>
       </c>
       <c r="I51" t="n">
         <v>-0.0286</v>
@@ -2802,7 +2802,7 @@
         <v>-0.0517</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4546</v>
+        <v>-0.4767</v>
       </c>
       <c r="E52" t="n">
         <v>-0.0822</v>
@@ -2842,25 +2842,25 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.0893</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0562</v>
+        <v>-0.0556</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4574</v>
+        <v>-0.4791</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.0893</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.0893</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.0893</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="I53" t="n">
         <v>-0.0906</v>
@@ -2888,25 +2888,25 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.2046</v>
+        <v>-0.2039</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1288</v>
+        <v>-0.1283</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.504</v>
+        <v>-0.5251</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.2046</v>
+        <v>-0.2039</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.2046</v>
+        <v>-0.2039</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.2046</v>
+        <v>-0.2039</v>
       </c>
       <c r="I54" t="n">
         <v>-0.2056</v>
@@ -2934,25 +2934,25 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.2669</v>
+        <v>-0.2649</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.168</v>
+        <v>-0.1667</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5292</v>
+        <v>-0.5494</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.2669</v>
+        <v>-0.2649</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.2669</v>
+        <v>-0.2649</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.2669</v>
+        <v>-0.2649</v>
       </c>
       <c r="I55" t="n">
         <v>-0.2694</v>
@@ -2980,25 +2980,25 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.376</v>
+        <v>-0.3745</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.2367</v>
+        <v>-0.2357</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5733</v>
+        <v>-0.5931</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.376</v>
+        <v>-0.3745</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.376</v>
+        <v>-0.3745</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.376</v>
+        <v>-0.3745</v>
       </c>
       <c r="I56" t="n">
         <v>-0.3777</v>
@@ -3026,25 +3026,25 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.407</v>
+        <v>-0.4055</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.2562</v>
+        <v>-0.2552</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5858</v>
+        <v>-0.6055</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.407</v>
+        <v>-0.4055</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.407</v>
+        <v>-0.4055</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.407</v>
+        <v>-0.4055</v>
       </c>
       <c r="I57" t="n">
         <v>-0.4089</v>
@@ -3072,25 +3072,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.4554</v>
+        <v>-0.4537</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.2866</v>
+        <v>-0.2856</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6052999999999999</v>
+        <v>-0.6247</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.4554</v>
+        <v>-0.4537</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.4554</v>
+        <v>-0.4537</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.4554</v>
+        <v>-0.4537</v>
       </c>
       <c r="I58" t="n">
         <v>-0.4575</v>
@@ -3118,25 +3118,25 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.519</v>
+        <v>-0.5152</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.3267</v>
+        <v>-0.3243</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.631</v>
+        <v>-0.6492</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.519</v>
+        <v>-0.5152</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.2083</v>
+        <v>-0.2045</v>
       </c>
       <c r="G59" t="n">
         <v>-0.3107</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.2083</v>
+        <v>-0.2045</v>
       </c>
       <c r="I59" t="n">
         <v>-0.2132</v>
@@ -3170,7 +3170,7 @@
         <v>-0.3719</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6601</v>
+        <v>-0.6793</v>
       </c>
       <c r="E60" t="n">
         <v>-0.5909</v>
@@ -3210,25 +3210,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.6169</v>
+        <v>-0.6055</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.3883</v>
+        <v>-0.3811</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6706</v>
+        <v>-0.6851</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.6169</v>
+        <v>-0.6055</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.6169</v>
+        <v>-0.6055</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.6169</v>
+        <v>-0.6055</v>
       </c>
       <c r="I61" t="n">
         <v>-0.6314</v>
@@ -3256,25 +3256,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.6567</v>
+        <v>-0.6445</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.4133</v>
+        <v>-0.4056</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6867</v>
+        <v>-0.7007</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.6567</v>
+        <v>-0.6445</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.6567</v>
+        <v>-0.6445</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.6567</v>
+        <v>-0.6445</v>
       </c>
       <c r="I62" t="n">
         <v>-0.6721</v>
@@ -3302,25 +3302,25 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.6983</v>
+        <v>-0.6931</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.4395</v>
+        <v>-0.4362</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7035</v>
+        <v>-0.72</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.6983</v>
+        <v>-0.6931</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.6983</v>
+        <v>-0.6931</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.6983</v>
+        <v>-0.6931</v>
       </c>
       <c r="I63" t="n">
         <v>-0.7048</v>
@@ -3348,25 +3348,25 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.7302</v>
+        <v>-0.7275</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.4596</v>
+        <v>-0.4579</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7163</v>
+        <v>-0.7337</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.7302</v>
+        <v>-0.7275</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.7302</v>
+        <v>-0.7275</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.7302</v>
+        <v>-0.7275</v>
       </c>
       <c r="I64" t="n">
         <v>-0.7336</v>
@@ -3394,25 +3394,25 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.7338</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.4619</v>
+        <v>-0.4584</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7178</v>
+        <v>-0.7341</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.7338</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.7338</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.7338</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="I65" t="n">
         <v>-0.7406</v>
@@ -3440,25 +3440,25 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.7375</v>
+        <v>-0.732</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.4642</v>
+        <v>-0.4607</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7193000000000001</v>
+        <v>-0.7355</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.7375</v>
+        <v>-0.732</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.7375</v>
+        <v>-0.732</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.7375</v>
+        <v>-0.732</v>
       </c>
       <c r="I66" t="n">
         <v>-0.7444</v>
@@ -3486,25 +3486,25 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.9607</v>
+        <v>-0.9536</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.6047</v>
+        <v>-0.6002</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8095</v>
+        <v>-0.8238</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.9607</v>
+        <v>-0.9536</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.9607</v>
+        <v>-0.9536</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.9607</v>
+        <v>-0.9536</v>
       </c>
       <c r="I67" t="n">
         <v>-0.9697</v>
@@ -3532,25 +3532,25 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.9892</v>
+        <v>-0.9782</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.6226</v>
+        <v>-0.6157</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.821</v>
+        <v>-0.8336</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.9892</v>
+        <v>-0.9782</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.9892</v>
+        <v>-0.9782</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.9892</v>
+        <v>-0.9782</v>
       </c>
       <c r="I68" t="n">
         <v>-1.0031</v>
@@ -3578,25 +3578,25 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.1224</v>
+        <v>-1.1141</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.7064</v>
+        <v>-0.7012</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8748</v>
+        <v>-0.8878</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.1224</v>
+        <v>-1.1141</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.1224</v>
+        <v>-1.1141</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-1.1224</v>
+        <v>-1.1141</v>
       </c>
       <c r="I69" t="n">
         <v>-1.1329</v>
@@ -3630,7 +3630,7 @@
         <v>-0.7168</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8814</v>
+        <v>-0.8976</v>
       </c>
       <c r="E70" t="n">
         <v>-1.1388</v>
@@ -3670,25 +3670,25 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.4046</v>
+        <v>-1.3993</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.8841</v>
+        <v>-0.8807</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9888</v>
+        <v>-1.0014</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.4046</v>
+        <v>-1.3993</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.4046</v>
+        <v>-1.3993</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-1.4046</v>
+        <v>-1.3993</v>
       </c>
       <c r="I71" t="n">
         <v>-1.4111</v>
@@ -3722,7 +3722,7 @@
         <v>-1.0485</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0943</v>
+        <v>-1.1076</v>
       </c>
       <c r="E72" t="n">
         <v>-1.6658</v>
@@ -3762,25 +3762,25 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.7399</v>
+        <v>-1.7269</v>
       </c>
       <c r="C73" t="n">
-        <v>-1.0951</v>
+        <v>-1.0869</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.1242</v>
+        <v>-1.1319</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.7399</v>
+        <v>-1.7269</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.7399</v>
+        <v>-1.7269</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.7399</v>
+        <v>-1.7269</v>
       </c>
       <c r="I73" t="n">
         <v>-1.7561</v>
@@ -3808,25 +3808,25 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.7982</v>
+        <v>-1.7915</v>
       </c>
       <c r="C74" t="n">
-        <v>-1.1318</v>
+        <v>-1.1276</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.1478</v>
+        <v>-1.1576</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.7982</v>
+        <v>-1.7915</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.7982</v>
+        <v>-1.7915</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.7982</v>
+        <v>-1.7915</v>
       </c>
       <c r="I74" t="n">
         <v>-1.8066</v>
@@ -3854,25 +3854,25 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.881</v>
+        <v>-1.8406</v>
       </c>
       <c r="C75" t="n">
-        <v>-1.1839</v>
+        <v>-1.1585</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1812</v>
+        <v>-1.1772</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.881</v>
+        <v>-1.8406</v>
       </c>
       <c r="F75" t="n">
-        <v>-2.1834</v>
+        <v>-2.143</v>
       </c>
       <c r="G75" t="n">
         <v>0.3024</v>
       </c>
       <c r="H75" t="n">
-        <v>-2.1834</v>
+        <v>-2.143</v>
       </c>
       <c r="I75" t="n">
         <v>-2.2347</v>
@@ -3900,25 +3900,25 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.9526</v>
+        <v>-1.9453</v>
       </c>
       <c r="C76" t="n">
-        <v>-1.229</v>
+        <v>-1.2244</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.2102</v>
+        <v>-1.2189</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.9526</v>
+        <v>-1.9453</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.9526</v>
+        <v>-1.9453</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.9526</v>
+        <v>-1.9453</v>
       </c>
       <c r="I76" t="n">
         <v>-1.9617</v>
@@ -3946,25 +3946,25 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-2.1076</v>
+        <v>-2.0686</v>
       </c>
       <c r="C77" t="n">
-        <v>-1.3265</v>
+        <v>-1.302</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.2728</v>
+        <v>-1.268</v>
       </c>
       <c r="E77" t="n">
-        <v>-2.1076</v>
+        <v>-2.0686</v>
       </c>
       <c r="F77" t="n">
-        <v>-2.1076</v>
+        <v>-2.0686</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-2.1076</v>
+        <v>-2.0686</v>
       </c>
       <c r="I77" t="n">
         <v>-2.1571</v>
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-2.1675</v>
+        <v>-2.1513</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.3642</v>
+        <v>-1.354</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.297</v>
+        <v>-1.301</v>
       </c>
       <c r="E78" t="n">
-        <v>-2.1675</v>
+        <v>-2.1513</v>
       </c>
       <c r="F78" t="n">
-        <v>-2.1675</v>
+        <v>-2.1513</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-2.1675</v>
+        <v>-2.1513</v>
       </c>
       <c r="I78" t="n">
         <v>-2.1877</v>
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.6157</v>
+        <v>-2.5962</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.6463</v>
+        <v>-1.634</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.478</v>
+        <v>-1.4782</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.6157</v>
+        <v>-2.5962</v>
       </c>
       <c r="F79" t="n">
-        <v>-2.6157</v>
+        <v>-2.5962</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-2.6157</v>
+        <v>-2.5962</v>
       </c>
       <c r="I79" t="n">
         <v>-2.6401</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-3.5401</v>
+        <v>-3.5004</v>
       </c>
       <c r="C80" t="n">
-        <v>-2.2281</v>
+        <v>-2.2031</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.8515</v>
+        <v>-1.8385</v>
       </c>
       <c r="E80" t="n">
-        <v>-3.5401</v>
+        <v>-3.5004</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.5401</v>
+        <v>-1.5004</v>
       </c>
       <c r="G80" t="n">
         <v>-2</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.5401</v>
+        <v>-1.5004</v>
       </c>
       <c r="I80" t="n">
         <v>-1.591</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3.6564</v>
+        <v>-3.562</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.3013</v>
+        <v>-2.2419</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.8985</v>
+        <v>-1.863</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.6564</v>
+        <v>-3.562</v>
       </c>
       <c r="F81" t="n">
-        <v>-3.6564</v>
+        <v>-3.562</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-3.6564</v>
+        <v>-3.562</v>
       </c>
       <c r="I81" t="n">
         <v>-3.7772</v>
@@ -4176,25 +4176,25 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-3.6743</v>
+        <v>-3.6063</v>
       </c>
       <c r="C82" t="n">
-        <v>-2.3126</v>
+        <v>-2.2698</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.9057</v>
+        <v>-1.8807</v>
       </c>
       <c r="E82" t="n">
-        <v>-3.6743</v>
+        <v>-3.6063</v>
       </c>
       <c r="F82" t="n">
-        <v>-3.6743</v>
+        <v>-3.6063</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>-3.6743</v>
+        <v>-3.6063</v>
       </c>
       <c r="I82" t="n">
         <v>-3.7606</v>
